--- a/stacked_model/results/validation/model_a_controls_only_summary.xlsx
+++ b/stacked_model/results/validation/model_a_controls_only_summary.xlsx
@@ -553,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01</v>
+        <v>1e-10</v>
       </c>
       <c r="F2" t="n">
         <v>50</v>
@@ -562,40 +562,40 @@
         <v>1900</v>
       </c>
       <c r="H2" t="n">
-        <v>3.869695260128584</v>
+        <v>3.781730755886398</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6614971667057515</v>
+        <v>0.6421504607242831</v>
       </c>
       <c r="J2" t="n">
-        <v>5.831125661760646</v>
+        <v>5.678499689998842</v>
       </c>
       <c r="K2" t="n">
-        <v>1.463414335233759</v>
+        <v>1.45241162822555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8131120643046106</v>
+        <v>0.8205451962565785</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1054519059712822</v>
+        <v>0.1021510297250552</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8684210526315791</v>
+        <v>0.8847368421052632</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07270330678877336</v>
+        <v>0.06970415503730491</v>
       </c>
       <c r="P2" t="n">
-        <v>3.233243797230067</v>
+        <v>3.150145626752687</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4147755760654275</v>
+        <v>0.2862200660165098</v>
       </c>
       <c r="R2" t="n">
-        <v>-92.96350938255723</v>
+        <v>-93.19370490582287</v>
       </c>
       <c r="S2" t="n">
-        <v>8.131850992794961</v>
+        <v>8.152461095298786</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -627,40 +627,40 @@
         <v>1900</v>
       </c>
       <c r="H3" t="n">
-        <v>3.880691463914166</v>
+        <v>3.781730819754383</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6652731973711774</v>
+        <v>0.6421505297902222</v>
       </c>
       <c r="J3" t="n">
-        <v>5.848690223450014</v>
+        <v>5.678499830461164</v>
       </c>
       <c r="K3" t="n">
-        <v>1.468938699423261</v>
+        <v>1.452411696371051</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8121401444958813</v>
+        <v>0.8205451884644828</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1053347451528176</v>
+        <v>0.1021510253132246</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8826315789473683</v>
+        <v>0.8847368421052632</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06792141791670174</v>
+        <v>0.06970415503730491</v>
       </c>
       <c r="P3" t="n">
-        <v>3.171975169520583</v>
+        <v>3.150148976798064</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2942978670779252</v>
+        <v>0.2862252188008217</v>
       </c>
       <c r="R3" t="n">
-        <v>-92.95479465443761</v>
+        <v>-93.19370490589679</v>
       </c>
       <c r="S3" t="n">
-        <v>8.127283327056023</v>
+        <v>8.152461095332256</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1e-10</v>
+        <v>0.01</v>
       </c>
       <c r="F4" t="n">
         <v>50</v>
@@ -692,40 +692,40 @@
         <v>1900</v>
       </c>
       <c r="H4" t="n">
-        <v>3.880691536142448</v>
+        <v>3.786504429129417</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6652731242817281</v>
+        <v>0.6489169951341316</v>
       </c>
       <c r="J4" t="n">
-        <v>5.848690238916125</v>
+        <v>5.696376857724666</v>
       </c>
       <c r="K4" t="n">
-        <v>1.468938684284019</v>
+        <v>1.477479220300409</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8121401438813309</v>
+        <v>0.8193288369469472</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1053347443914457</v>
+        <v>0.1031527234910025</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8826315789473683</v>
+        <v>0.8715789473684211</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06792141791670174</v>
+        <v>0.07145626689032614</v>
       </c>
       <c r="P4" t="n">
-        <v>3.171971484229076</v>
+        <v>3.21041114903842</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2942916433652344</v>
+        <v>0.3772340498713238</v>
       </c>
       <c r="R4" t="n">
-        <v>-92.95479465450211</v>
+        <v>-93.1784359849849</v>
       </c>
       <c r="S4" t="n">
-        <v>8.127283327091485</v>
+        <v>8.143382553930598</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -757,40 +757,40 @@
         <v>1900</v>
       </c>
       <c r="H5" t="n">
-        <v>3.938294558845263</v>
+        <v>3.822313993705845</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6864521465517048</v>
+        <v>0.6877575040096144</v>
       </c>
       <c r="J5" t="n">
-        <v>5.93864587207969</v>
+        <v>5.745462982056532</v>
       </c>
       <c r="K5" t="n">
-        <v>1.45804830478359</v>
+        <v>1.482832528485499</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8066334949149474</v>
+        <v>0.8160363935009392</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1050151468291599</v>
+        <v>0.1039222144949702</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8647368421052631</v>
+        <v>0.8689473684210526</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07367078287963913</v>
+        <v>0.07357095792473585</v>
       </c>
       <c r="P5" t="n">
-        <v>3.26153585500976</v>
+        <v>3.245053784659012</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4234301526611098</v>
+        <v>0.4298049984536266</v>
       </c>
       <c r="R5" t="n">
-        <v>-92.88090394897633</v>
+        <v>-93.07681626253216</v>
       </c>
       <c r="S5" t="n">
-        <v>8.097595733086363</v>
+        <v>8.140796726164378</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -813,7 +813,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>1e-10</v>
+        <v>1e-06</v>
       </c>
       <c r="F6" t="n">
         <v>50</v>
@@ -822,40 +822,40 @@
         <v>1900</v>
       </c>
       <c r="H6" t="n">
-        <v>3.938295141680098</v>
+        <v>3.822314241277788</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6864542609557979</v>
+        <v>0.6877586826874507</v>
       </c>
       <c r="J6" t="n">
-        <v>5.938646690773604</v>
+        <v>5.745463455870857</v>
       </c>
       <c r="K6" t="n">
-        <v>1.458050029227966</v>
+        <v>1.482834269731796</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8066334027232115</v>
+        <v>0.8160363316253606</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1050152919718952</v>
+        <v>0.103922341947172</v>
       </c>
       <c r="N6" t="n">
-        <v>0.88</v>
+        <v>0.8826315789473683</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06894371961712872</v>
+        <v>0.07254957309507695</v>
       </c>
       <c r="P6" t="n">
-        <v>3.194643339313186</v>
+        <v>3.181487701061981</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3040886706959394</v>
+        <v>0.3258600715067322</v>
       </c>
       <c r="R6" t="n">
-        <v>-92.88090395030646</v>
+        <v>-93.07681622748819</v>
       </c>
       <c r="S6" t="n">
-        <v>8.097595733221217</v>
+        <v>8.140796736900231</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -878,7 +878,7 @@
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>1e-06</v>
+        <v>1e-10</v>
       </c>
       <c r="F7" t="n">
         <v>50</v>
@@ -887,40 +887,40 @@
         <v>1900</v>
       </c>
       <c r="H7" t="n">
-        <v>3.938296288390266</v>
+        <v>3.822315091914536</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6864542911920775</v>
+        <v>0.6877610048092768</v>
       </c>
       <c r="J7" t="n">
-        <v>5.938648737015545</v>
+        <v>5.745463703924885</v>
       </c>
       <c r="K7" t="n">
-        <v>1.458049381038027</v>
+        <v>1.482834092887398</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8066332743587187</v>
+        <v>0.8160363215695114</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1050152763743381</v>
+        <v>0.1039223279483686</v>
       </c>
       <c r="N7" t="n">
-        <v>0.88</v>
+        <v>0.8826315789473683</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06894371961712872</v>
+        <v>0.07254957309507695</v>
       </c>
       <c r="P7" t="n">
-        <v>3.194648080136794</v>
+        <v>3.181483453815591</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3040958745270748</v>
+        <v>0.3258523237800394</v>
       </c>
       <c r="R7" t="n">
-        <v>-92.88090395072896</v>
+        <v>-93.07681622287423</v>
       </c>
       <c r="S7" t="n">
-        <v>8.097595733356362</v>
+        <v>8.140796738274695</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01</v>
+        <v>1e-10</v>
       </c>
       <c r="F8" t="n">
         <v>50</v>
@@ -952,40 +952,40 @@
         <v>1900</v>
       </c>
       <c r="H8" t="n">
-        <v>4.241557555463249</v>
+        <v>4.19553354053343</v>
       </c>
       <c r="I8" t="n">
-        <v>0.71107258352709</v>
+        <v>0.680133874029153</v>
       </c>
       <c r="J8" t="n">
-        <v>6.092020955586945</v>
+        <v>5.973222427153738</v>
       </c>
       <c r="K8" t="n">
-        <v>1.480047540890516</v>
+        <v>1.41134558896239</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7971520264292173</v>
+        <v>0.8034126470840408</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1109332819397375</v>
+        <v>0.1043822972291243</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8478947368421053</v>
+        <v>0.8673684210526317</v>
       </c>
       <c r="O8" t="n">
-        <v>0.07039015665154243</v>
+        <v>0.07230565582057928</v>
       </c>
       <c r="P8" t="n">
-        <v>3.229902715246915</v>
+        <v>3.188811346733944</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3457834982924182</v>
+        <v>0.2867443607334661</v>
       </c>
       <c r="R8" t="n">
-        <v>-97.47645457877761</v>
+        <v>-97.72737495188591</v>
       </c>
       <c r="S8" t="n">
-        <v>7.546256350248373</v>
+        <v>7.547853000719799</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1017,40 +1017,40 @@
         <v>1900</v>
       </c>
       <c r="H9" t="n">
-        <v>4.244666028403588</v>
+        <v>4.195533441819518</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7071111125592207</v>
+        <v>0.6801348280233869</v>
       </c>
       <c r="J9" t="n">
-        <v>6.094289981315016</v>
+        <v>5.973223395891116</v>
       </c>
       <c r="K9" t="n">
-        <v>1.477044070181857</v>
+        <v>1.411347384448408</v>
       </c>
       <c r="L9" t="n">
-        <v>0.797043964117639</v>
+        <v>0.803412547866906</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1108303573592058</v>
+        <v>0.1043825802976856</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8668421052631579</v>
+        <v>0.8673684210526317</v>
       </c>
       <c r="O9" t="n">
-        <v>0.07180549540718342</v>
+        <v>0.07230565582057928</v>
       </c>
       <c r="P9" t="n">
-        <v>3.198741011842143</v>
+        <v>3.188813618139309</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3029457719038903</v>
+        <v>0.2867470424563529</v>
       </c>
       <c r="R9" t="n">
-        <v>-97.47310475702268</v>
+        <v>-97.72737496078261</v>
       </c>
       <c r="S9" t="n">
-        <v>7.543674565185135</v>
+        <v>7.547853003987138</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1e-10</v>
+        <v>0.01</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
@@ -1082,40 +1082,40 @@
         <v>1900</v>
       </c>
       <c r="H10" t="n">
-        <v>4.244671121998336</v>
+        <v>4.196745735211449</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7071058506176005</v>
+        <v>0.6959562332324236</v>
       </c>
       <c r="J10" t="n">
-        <v>6.09429532278673</v>
+        <v>5.9941923594051</v>
       </c>
       <c r="K10" t="n">
-        <v>1.477039151377521</v>
+        <v>1.423704245645634</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7970437106131461</v>
+        <v>0.8020590840049026</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1108301632076046</v>
+        <v>0.1047867860732239</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8668421052631579</v>
+        <v>0.8521052631578947</v>
       </c>
       <c r="O10" t="n">
-        <v>0.07180549540718342</v>
+        <v>0.0701084983270843</v>
       </c>
       <c r="P10" t="n">
-        <v>3.198739116136922</v>
+        <v>3.226070556457095</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3029421200677613</v>
+        <v>0.3285094337176734</v>
       </c>
       <c r="R10" t="n">
-        <v>-97.4731047646718</v>
+        <v>-97.70057325484892</v>
       </c>
       <c r="S10" t="n">
-        <v>7.543674567494045</v>
+        <v>7.550715739555349</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -1147,40 +1147,40 @@
         <v>1900</v>
       </c>
       <c r="H11" t="n">
-        <v>4.286620365209236</v>
+        <v>4.275525773267599</v>
       </c>
       <c r="I11" t="n">
-        <v>0.706023262673242</v>
+        <v>0.696219299762042</v>
       </c>
       <c r="J11" t="n">
-        <v>6.161112910023</v>
+        <v>6.100282400365196</v>
       </c>
       <c r="K11" t="n">
-        <v>1.442977942224819</v>
+        <v>1.37776855370589</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7927908779211787</v>
+        <v>0.7953482982790269</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1101986207933</v>
+        <v>0.1042717460616921</v>
       </c>
       <c r="N11" t="n">
         <v>0.8610526315789474</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06953159712298883</v>
+        <v>0.0748186417904293</v>
       </c>
       <c r="P11" t="n">
-        <v>3.221090515610791</v>
+        <v>3.219437332801541</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2975773250393094</v>
+        <v>0.295946422618875</v>
       </c>
       <c r="R11" t="n">
-        <v>-97.30129390313978</v>
+        <v>-97.53672070450537</v>
       </c>
       <c r="S11" t="n">
-        <v>7.477158228326291</v>
+        <v>7.51161032432415</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1212,40 +1212,40 @@
         <v>1900</v>
       </c>
       <c r="H12" t="n">
-        <v>4.30461874523414</v>
+        <v>4.275709365365421</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7155191774415022</v>
+        <v>0.6961604047212788</v>
       </c>
       <c r="J12" t="n">
-        <v>6.197028354871878</v>
+        <v>6.100742720910757</v>
       </c>
       <c r="K12" t="n">
-        <v>1.443947463717196</v>
+        <v>1.377430467092685</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7907261437481716</v>
+        <v>0.7953228108144491</v>
       </c>
       <c r="M12" t="n">
-        <v>0.109747226587782</v>
+        <v>0.1042559933682687</v>
       </c>
       <c r="N12" t="n">
         <v>0.8610526315789474</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06953159712298883</v>
+        <v>0.0748186417904293</v>
       </c>
       <c r="P12" t="n">
-        <v>3.224978283858681</v>
+        <v>3.220998862712821</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2973808480908679</v>
+        <v>0.2954236447563436</v>
       </c>
       <c r="R12" t="n">
-        <v>-97.31113296629063</v>
+        <v>-97.51386009565137</v>
       </c>
       <c r="S12" t="n">
-        <v>7.477395825821525</v>
+        <v>7.507754883702987</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1277,40 +1277,40 @@
         <v>1900</v>
       </c>
       <c r="H13" t="n">
-        <v>4.30986444869051</v>
+        <v>4.280546913967818</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7078644558057595</v>
+        <v>0.7072039367001662</v>
       </c>
       <c r="J13" t="n">
-        <v>6.203690679830312</v>
+        <v>6.110863684376735</v>
       </c>
       <c r="K13" t="n">
-        <v>1.435672142916673</v>
+        <v>1.395350547687038</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7904043980533315</v>
+        <v>0.7943976598076585</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1094419460886547</v>
+        <v>0.1059108698707406</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8431578947368421</v>
+        <v>0.8478947368421053</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06890270853764636</v>
+        <v>0.07138700808945592</v>
       </c>
       <c r="P13" t="n">
-        <v>3.263806773328233</v>
+        <v>3.258874116225943</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3364356840721859</v>
+        <v>0.3435624246141789</v>
       </c>
       <c r="R13" t="n">
-        <v>-97.28259438186711</v>
+        <v>-97.51588070696671</v>
       </c>
       <c r="S13" t="n">
-        <v>7.462666543302724</v>
+        <v>7.504877567857443</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
